--- a/May_5_full_log/LHS_HRP_1_res.xlsx
+++ b/May_5_full_log/LHS_HRP_1_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\May_5_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABC198D-4D28-4C5B-A2E3-092E1474CDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFCA501-D209-4DF8-8B54-732904EC38A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>HRP</t>
+  </si>
   <si>
     <t>TMB</t>
   </si>
   <si>
     <t>H2O2</t>
+  </si>
+  <si>
+    <t>max_intensity</t>
+  </si>
+  <si>
+    <t>reaction_speed</t>
+  </si>
+  <si>
+    <t>color_retention</t>
   </si>
   <si>
     <t>AUC</t>
@@ -396,10 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,362 +421,2966 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>0.66796475099999997</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>0.13890091399999999</v>
       </c>
-      <c r="C2">
-        <v>14194.669627749579</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>103.0065989847716</v>
+      </c>
+      <c r="E2">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F2">
+        <v>0.94806798637906797</v>
+      </c>
+      <c r="G2">
+        <v>11835.703045685281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.66796475099999997</v>
+      </c>
+      <c r="C3">
+        <v>0.13890091399999999</v>
+      </c>
+      <c r="D3">
+        <v>102.358883248731</v>
+      </c>
+      <c r="E3">
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="F3">
+        <v>0.94181614405371794</v>
+      </c>
+      <c r="G3">
+        <v>11715.29923857868</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>0.72159662800000002</v>
+      </c>
+      <c r="C4">
+        <v>0.41392194599999999</v>
+      </c>
+      <c r="D4">
+        <v>102.5147208121828</v>
+      </c>
+      <c r="E4">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F4">
+        <v>0.92269526723907414</v>
+      </c>
+      <c r="G4">
+        <v>11610.999238578681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0.66796475099999997</v>
+      </c>
+      <c r="C5">
+        <v>0.13890091399999999</v>
+      </c>
+      <c r="D5">
+        <v>101.2553299492384</v>
+      </c>
+      <c r="E5">
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="F5">
+        <v>0.93224646944699308</v>
+      </c>
+      <c r="G5">
+        <v>11509.58401015229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>0.66796475099999997</v>
+      </c>
+      <c r="C6">
+        <v>0.13890091399999999</v>
+      </c>
+      <c r="D6">
+        <v>101.8197969543146</v>
+      </c>
+      <c r="E6">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F6">
+        <v>0.89338484931575202</v>
+      </c>
+      <c r="G6">
+        <v>11464.122081218269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>0.282070926</v>
+      </c>
+      <c r="C7">
+        <v>5.3319099999999996E-3</v>
+      </c>
+      <c r="D7">
+        <v>99.921319796954208</v>
+      </c>
+      <c r="E7">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F7">
+        <v>0.62021997002717943</v>
+      </c>
+      <c r="G7">
+        <v>9963.9532994923884</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>0.39120680400000002</v>
       </c>
-      <c r="B3">
+      <c r="C8">
         <v>3.2509787999999998E-2</v>
       </c>
-      <c r="C3">
-        <v>10622.659475465311</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="D8">
+        <v>90.629949238578817</v>
+      </c>
+      <c r="E8">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F8">
+        <v>0.85598377963604877</v>
+      </c>
+      <c r="G8">
+        <v>9571.4703045685274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>0.39120680400000002</v>
+      </c>
+      <c r="C9">
+        <v>3.2509787999999998E-2</v>
+      </c>
+      <c r="D9">
+        <v>94.850761421319817</v>
+      </c>
+      <c r="E9">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F9">
+        <v>0.74013786017039862</v>
+      </c>
+      <c r="G9">
+        <v>9477.2403553299482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
         <v>0.282070926</v>
       </c>
-      <c r="B4">
+      <c r="C10">
         <v>5.3319099999999996E-3</v>
       </c>
-      <c r="C4">
-        <v>10412.25296108291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="D10">
+        <v>91.208121827411205</v>
+      </c>
+      <c r="E10">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F10">
+        <v>0.56582368655387383</v>
+      </c>
+      <c r="G10">
+        <v>8395.9934010152301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>0.282070926</v>
+      </c>
+      <c r="C11">
+        <v>5.3319099999999996E-3</v>
+      </c>
+      <c r="D11">
+        <v>85.936548223350414</v>
+      </c>
+      <c r="E11">
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="F11">
+        <v>0.55851738090315628</v>
+      </c>
+      <c r="G11">
+        <v>7867.1324873096464</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
         <v>0.97711959400000004</v>
       </c>
-      <c r="B5">
+      <c r="C12">
         <v>0.59509776999999997</v>
       </c>
-      <c r="C5">
-        <v>9441.4763113367171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="D12">
+        <v>102.986802030457</v>
+      </c>
+      <c r="E12">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F12">
+        <v>0.72777054868791946</v>
+      </c>
+      <c r="G12">
+        <v>7518.5479695431486</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>0.97711959400000004</v>
+      </c>
+      <c r="C13">
+        <v>0.59509776999999997</v>
+      </c>
+      <c r="D13">
+        <v>103.7147208121828</v>
+      </c>
+      <c r="E13">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F13">
+        <v>0.70580957135445688</v>
+      </c>
+      <c r="G13">
+        <v>7439.0205583756342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>0.282070926</v>
+      </c>
+      <c r="C14">
+        <v>5.3319099999999996E-3</v>
+      </c>
+      <c r="D14">
+        <v>73.445685279187828</v>
+      </c>
+      <c r="E14">
+        <v>0.95798319327731096</v>
+      </c>
+      <c r="F14">
+        <v>0.65950458918500499</v>
+      </c>
+      <c r="G14">
+        <v>7090.6182741116736</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
         <v>0.72159662800000002</v>
       </c>
-      <c r="B6">
+      <c r="C15">
         <v>0.41392194599999999</v>
       </c>
-      <c r="C6">
-        <v>8689.7707275803714</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="D15">
+        <v>101.4730964467004</v>
+      </c>
+      <c r="E15">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F15">
+        <v>0.56497883963141993</v>
+      </c>
+      <c r="G15">
+        <v>6840.1657360406107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>0.45884837899999997</v>
+      </c>
+      <c r="C16">
+        <v>0.18962421700000001</v>
+      </c>
+      <c r="D16">
+        <v>102.043654822335</v>
+      </c>
+      <c r="E16">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F16">
+        <v>8.6244565379602622E-2</v>
+      </c>
+      <c r="G16">
+        <v>6665.3312182741138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
         <v>0.59911378199999998</v>
       </c>
-      <c r="B7">
+      <c r="C17">
         <v>2.2434213000000001E-2</v>
       </c>
-      <c r="C7">
-        <v>7049.5283417935707</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="D17">
+        <v>56.808629441624362</v>
+      </c>
+      <c r="E17">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F17">
+        <v>0.99670637012679497</v>
+      </c>
+      <c r="G17">
+        <v>6397.402030456853</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>0.72159662800000002</v>
+      </c>
+      <c r="C18">
+        <v>0.41392194599999999</v>
+      </c>
+      <c r="D18">
+        <v>77.732487309644839</v>
+      </c>
+      <c r="E18">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F18">
+        <v>0.63393259454199802</v>
+      </c>
+      <c r="G18">
+        <v>5807.2827411167527</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>0.72159662800000002</v>
+      </c>
+      <c r="C19">
+        <v>0.41392194599999999</v>
+      </c>
+      <c r="D19">
+        <v>97.414720812182807</v>
+      </c>
+      <c r="E19">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F19">
+        <v>0.52899790002449076</v>
+      </c>
+      <c r="G19">
+        <v>5505.7142131979708</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>0.97711959400000004</v>
+      </c>
+      <c r="C20">
+        <v>0.59509776999999997</v>
+      </c>
+      <c r="D20">
+        <v>102.7370558375634</v>
+      </c>
+      <c r="E20">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F20">
+        <v>0.2819834776078109</v>
+      </c>
+      <c r="G20">
+        <v>5448.2456852791865</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>0.59911378199999998</v>
+      </c>
+      <c r="C21">
+        <v>2.2434213000000001E-2</v>
+      </c>
+      <c r="D21">
+        <v>47.529441624365489</v>
+      </c>
+      <c r="E21">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F21">
+        <v>0.99817372080356237</v>
+      </c>
+      <c r="G21">
+        <v>5275.6345177664989</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <v>0.39120680400000002</v>
+      </c>
+      <c r="C22">
+        <v>3.2509787999999998E-2</v>
+      </c>
+      <c r="D22">
+        <v>64.504060913705601</v>
+      </c>
+      <c r="E22">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F22">
+        <v>0.55097148882925506</v>
+      </c>
+      <c r="G22">
+        <v>4910.9946700507626</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
         <v>0.45884837899999997</v>
       </c>
-      <c r="B8">
+      <c r="C23">
         <v>0.18962421700000001</v>
       </c>
-      <c r="C8">
-        <v>6256.1890862944174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="D23">
+        <v>101.327918781726</v>
+      </c>
+      <c r="E23">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F23">
+        <v>5.4874358768836069E-2</v>
+      </c>
+      <c r="G23">
+        <v>4629.5225888324867</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>0.97711959400000004</v>
+      </c>
+      <c r="C24">
+        <v>0.59509776999999997</v>
+      </c>
+      <c r="D24">
+        <v>102.47817258883261</v>
+      </c>
+      <c r="E24">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F24">
+        <v>0.22841164640730699</v>
+      </c>
+      <c r="G24">
+        <v>4567.0365482233519</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25">
         <v>0.167990693</v>
       </c>
-      <c r="B9">
+      <c r="C25">
         <v>0.12664497999999999</v>
       </c>
-      <c r="C9">
-        <v>5069.0943316412859</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="D25">
+        <v>57.593908629441607</v>
+      </c>
+      <c r="E25">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F25">
+        <v>0.32579763793407401</v>
+      </c>
+      <c r="G25">
+        <v>4423.0441624365494</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26">
+        <v>0.39120680400000002</v>
+      </c>
+      <c r="C26">
+        <v>3.2509787999999998E-2</v>
+      </c>
+      <c r="D26">
+        <v>56.671065989847719</v>
+      </c>
+      <c r="E26">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F26">
+        <v>0.82728722165493285</v>
+      </c>
+      <c r="G26">
+        <v>4181.3337563451787</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <v>0.59911378199999998</v>
+      </c>
+      <c r="C27">
+        <v>2.2434213000000001E-2</v>
+      </c>
+      <c r="D27">
+        <v>36.023857868020308</v>
+      </c>
+      <c r="E27">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F27">
+        <v>0.99715924302844983</v>
+      </c>
+      <c r="G27">
+        <v>4051.899238578681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28">
+        <v>0.32734781499999999</v>
+      </c>
+      <c r="C28">
+        <v>0.24485045699999999</v>
+      </c>
+      <c r="D28">
+        <v>83.214213197969585</v>
+      </c>
+      <c r="E28">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F28">
+        <v>0.56149989019837476</v>
+      </c>
+      <c r="G28">
+        <v>3966.69416243655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>0.59911378199999998</v>
+      </c>
+      <c r="C29">
+        <v>2.2434213000000001E-2</v>
+      </c>
+      <c r="D29">
+        <v>34.721827411167517</v>
+      </c>
+      <c r="E29">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F29">
+        <v>0.94892547001549699</v>
+      </c>
+      <c r="G29">
+        <v>3946.9571065989858</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30">
+        <v>0.167990693</v>
+      </c>
+      <c r="C30">
+        <v>0.12664497999999999</v>
+      </c>
+      <c r="D30">
+        <v>49.932994923857862</v>
+      </c>
+      <c r="E30">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F30">
+        <v>0.26313028627195828</v>
+      </c>
+      <c r="G30">
+        <v>3525.2248730964479</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31">
         <v>0.23680810499999999</v>
       </c>
-      <c r="B10">
+      <c r="C31">
         <v>0.22312816499999999</v>
       </c>
-      <c r="C10">
-        <v>4779.5676818950933</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="D31">
+        <v>55.58223350253806</v>
+      </c>
+      <c r="E31">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F31">
+        <v>0.71370539832141533</v>
+      </c>
+      <c r="G31">
+        <v>3343.644416243656</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32">
+        <v>0.45884837899999997</v>
+      </c>
+      <c r="C32">
+        <v>0.18962421700000001</v>
+      </c>
+      <c r="D32">
+        <v>100.47715736040639</v>
+      </c>
+      <c r="E32">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F32">
+        <v>2.6572698797615521E-2</v>
+      </c>
+      <c r="G32">
+        <v>3332.361675126906</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33">
+        <v>0.141097525</v>
+      </c>
+      <c r="C33">
+        <v>1.3544883000000001E-2</v>
+      </c>
+      <c r="D33">
+        <v>29.588324873096461</v>
+      </c>
+      <c r="E33">
+        <v>0.94957983193277307</v>
+      </c>
+      <c r="F33">
+        <v>0.94098028787592802</v>
+      </c>
+      <c r="G33">
+        <v>3298.5837563451792</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
         <v>0.32734781499999999</v>
       </c>
-      <c r="B11">
+      <c r="C34">
         <v>0.24485045699999999</v>
       </c>
-      <c r="C11">
-        <v>4444.2931472081227</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="D34">
+        <v>76.729441624365506</v>
+      </c>
+      <c r="E34">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F34">
+        <v>0.52720681146093107</v>
+      </c>
+      <c r="G34">
+        <v>3153.1614213197981</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35">
+        <v>0.141097525</v>
+      </c>
+      <c r="C35">
+        <v>1.3544883000000001E-2</v>
+      </c>
+      <c r="D35">
+        <v>27.319289340101541</v>
+      </c>
+      <c r="E35">
+        <v>0.9327731092436975</v>
+      </c>
+      <c r="F35">
+        <v>0.90353592597409838</v>
+      </c>
+      <c r="G35">
+        <v>2982.5035532994939</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36">
+        <v>0.45884837899999997</v>
+      </c>
+      <c r="C36">
+        <v>0.18962421700000001</v>
+      </c>
+      <c r="D36">
+        <v>98.563959390863005</v>
+      </c>
+      <c r="E36">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F36">
+        <v>3.7012736196445413E-2</v>
+      </c>
+      <c r="G36">
+        <v>2884.7771573604068</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37">
+        <v>0.167990693</v>
+      </c>
+      <c r="C37">
+        <v>0.12664497999999999</v>
+      </c>
+      <c r="D37">
+        <v>48.035532994923877</v>
+      </c>
+      <c r="E37">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="F37">
+        <v>3.9237028426503361E-2</v>
+      </c>
+      <c r="G37">
+        <v>2223.5624365482249</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38">
+        <v>0.23680810499999999</v>
+      </c>
+      <c r="C38">
+        <v>0.22312816499999999</v>
+      </c>
+      <c r="D38">
+        <v>49.45025380710662</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>0.64593243479064233</v>
+      </c>
+      <c r="G38">
+        <v>2181.619035532995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39">
+        <v>0.23680810499999999</v>
+      </c>
+      <c r="C39">
+        <v>0.22312816499999999</v>
+      </c>
+      <c r="D39">
+        <v>52.220812182741128</v>
+      </c>
+      <c r="E39">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F39">
+        <v>0.57755334143377857</v>
+      </c>
+      <c r="G39">
+        <v>2169.4934010152292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40">
         <v>0.12037608599999999</v>
       </c>
-      <c r="B12">
+      <c r="C40">
         <v>1.2914360999999999E-2</v>
       </c>
-      <c r="C12">
-        <v>4387.991539763113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="D40">
+        <v>30.3319796954315</v>
+      </c>
+      <c r="E40">
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="F40">
+        <v>0.32977541252468451</v>
+      </c>
+      <c r="G40">
+        <v>2161.1753807106611</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41">
+        <v>0.23680810499999999</v>
+      </c>
+      <c r="C41">
+        <v>0.22312816499999999</v>
+      </c>
+      <c r="D41">
+        <v>42.700507614213222</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>0.73517593913456913</v>
+      </c>
+      <c r="G41">
+        <v>2091.2994923857868</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42">
+        <v>0.12037608599999999</v>
+      </c>
+      <c r="C42">
+        <v>1.2914360999999999E-2</v>
+      </c>
+      <c r="D42">
+        <v>24.456345177664989</v>
+      </c>
+      <c r="E42">
+        <v>0.95798319327731096</v>
+      </c>
+      <c r="F42">
+        <v>0.40927374997405541</v>
+      </c>
+      <c r="G42">
+        <v>1894.2317258883249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43">
+        <v>0.12037608599999999</v>
+      </c>
+      <c r="C43">
+        <v>1.2914360999999999E-2</v>
+      </c>
+      <c r="D43">
+        <v>23.666497461928941</v>
+      </c>
+      <c r="E43">
+        <v>0.95798319327731096</v>
+      </c>
+      <c r="F43">
+        <v>0.40723677155052218</v>
+      </c>
+      <c r="G43">
+        <v>1802.53959390863</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44">
+        <v>0.12037608599999999</v>
+      </c>
+      <c r="C44">
+        <v>1.2914360999999999E-2</v>
+      </c>
+      <c r="D44">
+        <v>22.715228426395949</v>
+      </c>
+      <c r="E44">
+        <v>0.97478991596638653</v>
+      </c>
+      <c r="F44">
+        <v>0.34653735279000658</v>
+      </c>
+      <c r="G44">
+        <v>1609.6459390862949</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45">
+        <v>0.167990693</v>
+      </c>
+      <c r="C45">
+        <v>0.12664497999999999</v>
+      </c>
+      <c r="D45">
+        <v>38.355837563451772</v>
+      </c>
+      <c r="E45">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F45">
+        <v>5.3347626421037478E-2</v>
+      </c>
+      <c r="G45">
+        <v>1582.9837563451781</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46">
+        <v>0.32734781499999999</v>
+      </c>
+      <c r="C46">
+        <v>0.24485045699999999</v>
+      </c>
+      <c r="D46">
+        <v>74.436040609137052</v>
+      </c>
+      <c r="E46">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F46">
+        <v>8.3947653761959617E-2</v>
+      </c>
+      <c r="G46">
+        <v>1143.74035532995</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47">
+        <v>0.32734781499999999</v>
+      </c>
+      <c r="C47">
+        <v>0.24485045699999999</v>
+      </c>
+      <c r="D47">
+        <v>75.056852791878029</v>
+      </c>
+      <c r="E47">
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="F47">
+        <v>9.4036331173662266E-2</v>
+      </c>
+      <c r="G47">
+        <v>1114.834771573604</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48">
+        <v>5.6199394E-2</v>
+      </c>
+      <c r="C48">
+        <v>0.10987182700000001</v>
+      </c>
+      <c r="D48">
+        <v>17.083248730964481</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>0.1406667855232665</v>
+      </c>
+      <c r="G48">
+        <v>871.21928934010225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49">
         <v>0.141097525</v>
       </c>
-      <c r="B13">
+      <c r="C49">
         <v>1.3544883000000001E-2</v>
       </c>
-      <c r="C13">
-        <v>4087.1945854483929</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="D49">
+        <v>11.62436548223352</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>837.77461928934054</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>1</v>
+      </c>
+      <c r="B50">
         <v>5.6199394E-2</v>
       </c>
-      <c r="B14">
+      <c r="C50">
         <v>0.10987182700000001</v>
       </c>
-      <c r="C14">
-        <v>3346.0630287648059</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="D50">
+        <v>16.048730964467019</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>0.1554149797570846</v>
+      </c>
+      <c r="G50">
+        <v>814.81294416243713</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>5.6199394E-2</v>
+      </c>
+      <c r="C51">
+        <v>0.10987182700000001</v>
+      </c>
+      <c r="D51">
+        <v>13.538578680203059</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>706.43350253807171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52">
         <v>0.21703388800000001</v>
       </c>
-      <c r="B15">
+      <c r="C52">
         <v>0.34830048800000002</v>
       </c>
-      <c r="C15">
-        <v>3134.7021996615908</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="D52">
+        <v>52.33147208121828</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>3.0339596286848441E-2</v>
+      </c>
+      <c r="G52">
+        <v>661.28781725888405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>1</v>
+      </c>
+      <c r="B53">
+        <v>5.6199394E-2</v>
+      </c>
+      <c r="C53">
+        <v>0.10987182700000001</v>
+      </c>
+      <c r="D53">
+        <v>10.52588832487308</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>659.26319796954351</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54">
+        <v>0.141097525</v>
+      </c>
+      <c r="C54">
+        <v>1.3544883000000001E-2</v>
+      </c>
+      <c r="D54">
+        <v>11.60761421319796</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>586.36091370558404</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55">
+        <v>0.21703388800000001</v>
+      </c>
+      <c r="C55">
+        <v>0.34830048800000002</v>
+      </c>
+      <c r="D55">
+        <v>44.870558375634523</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>3.6402511454267837E-2</v>
+      </c>
+      <c r="G55">
+        <v>524.90837563451851</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56">
+        <v>0.21703388800000001</v>
+      </c>
+      <c r="C56">
+        <v>0.34830048800000002</v>
+      </c>
+      <c r="D56">
+        <v>47.626903553299499</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>3.5964828137490093E-2</v>
+      </c>
+      <c r="G56">
+        <v>515.9020304568528</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>1</v>
+      </c>
+      <c r="B57">
+        <v>0.21703388800000001</v>
+      </c>
+      <c r="C57">
+        <v>0.34830048800000002</v>
+      </c>
+      <c r="D57">
+        <v>46.719289340101497</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>4.035550919738836E-2</v>
+      </c>
+      <c r="G57">
+        <v>468.21878172588907</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58">
         <v>3.3753191000000002E-2</v>
       </c>
-      <c r="B16">
+      <c r="C58">
         <v>9.4386890000000001E-3</v>
       </c>
-      <c r="C16">
-        <v>2910.944162436549</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="D58">
+        <v>7.054314720812183</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>432.16624365482272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59">
+        <v>3.3753191000000002E-2</v>
+      </c>
+      <c r="C59">
+        <v>9.4386890000000001E-3</v>
+      </c>
+      <c r="D59">
+        <v>7.185279187817244</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>387.09010152284282</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60">
         <v>5.7519069999999997E-3</v>
       </c>
-      <c r="B17">
+      <c r="C60">
         <v>0.65046243800000003</v>
       </c>
-      <c r="C17">
-        <v>2813.994500846024</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18">
+      <c r="D60">
+        <v>3.502538071065981</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>278.32436548223433</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61">
+        <v>3.3753191000000002E-2</v>
+      </c>
+      <c r="C61">
+        <v>9.4386890000000001E-3</v>
+      </c>
+      <c r="D61">
+        <v>4.8274111675127003</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>258.33654822335058</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62">
         <v>1.1870441000000001E-2</v>
       </c>
-      <c r="B18">
+      <c r="C62">
         <v>1.1121890000000001E-2</v>
       </c>
-      <c r="C18">
-        <v>2794.6620135363801</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="D62">
+        <v>3.742131979695444</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>249.92652284264031</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <v>5.7519069999999997E-3</v>
+      </c>
+      <c r="C63">
+        <v>0.65046243800000003</v>
+      </c>
+      <c r="D63">
+        <v>3.5274111675127031</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>249.6563451776654</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64">
+        <v>3.3753191000000002E-2</v>
+      </c>
+      <c r="C64">
+        <v>9.4386890000000001E-3</v>
+      </c>
+      <c r="D64">
+        <v>4.4812182741116828</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>233.2436548223354</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65">
+        <v>7.3565729999999996E-2</v>
+      </c>
+      <c r="C65">
+        <v>0.81115122299999998</v>
+      </c>
+      <c r="D65">
+        <v>11.681218274111689</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>222.28274111675191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>1</v>
+      </c>
+      <c r="B66">
+        <v>1.1870441000000001E-2</v>
+      </c>
+      <c r="C66">
+        <v>1.1121890000000001E-2</v>
+      </c>
+      <c r="D66">
+        <v>2.899492385786822</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>198.69111675126959</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>1</v>
+      </c>
+      <c r="B67">
+        <v>5.7519069999999997E-3</v>
+      </c>
+      <c r="C67">
+        <v>0.65046243800000003</v>
+      </c>
+      <c r="D67">
+        <v>2.5091370558375421</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>179.71015228426461</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68">
+        <v>1.1870441000000001E-2</v>
+      </c>
+      <c r="C68">
+        <v>1.1121890000000001E-2</v>
+      </c>
+      <c r="D68">
+        <v>3.390862944162421</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>176.40431472081269</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>1</v>
+      </c>
+      <c r="B69">
+        <v>1.1870441000000001E-2</v>
+      </c>
+      <c r="C69">
+        <v>1.1121890000000001E-2</v>
+      </c>
+      <c r="D69">
+        <v>2.8832487309644819</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>161.35532994923901</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>1</v>
+      </c>
+      <c r="B70">
+        <v>5.7519069999999997E-3</v>
+      </c>
+      <c r="C70">
+        <v>0.65046243800000003</v>
+      </c>
+      <c r="D70">
+        <v>2.481218274111701</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>161.33781725888349</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>1</v>
+      </c>
+      <c r="B71">
         <v>6.8150700000000003E-3</v>
       </c>
-      <c r="B19">
+      <c r="C71">
         <v>0.30638246699999999</v>
       </c>
-      <c r="C19">
-        <v>2726.5913705583762</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20">
+      <c r="D71">
+        <v>2.171065989847722</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>146.4885786802034</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>1</v>
+      </c>
+      <c r="B72">
+        <v>9.1106320000000005E-2</v>
+      </c>
+      <c r="C72">
+        <v>1.9513685999999999E-2</v>
+      </c>
+      <c r="D72">
+        <v>13.066497461928961</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>134.39619289340109</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73">
+        <v>6.8150700000000003E-3</v>
+      </c>
+      <c r="C73">
+        <v>0.30638246699999999</v>
+      </c>
+      <c r="D73">
+        <v>1.7959390862944209</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>131.28654822335051</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74">
+        <v>1.7124029999999998E-2</v>
+      </c>
+      <c r="C74">
+        <v>3.9181740999999999E-2</v>
+      </c>
+      <c r="D74">
+        <v>3.3182741116751018</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>115.00482233502539</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75">
         <v>7.3565729999999996E-2</v>
       </c>
-      <c r="B20">
+      <c r="C75">
         <v>0.81115122299999998</v>
       </c>
-      <c r="C20">
-        <v>2713.552453468697</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21">
+      <c r="D75">
+        <v>12.90253807106598</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>111.3449238578683</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76">
+        <v>7.3565729999999996E-2</v>
+      </c>
+      <c r="C76">
+        <v>0.81115122299999998</v>
+      </c>
+      <c r="D76">
+        <v>9.3106598984771871</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>89.690101522842937</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>1</v>
+      </c>
+      <c r="B77">
+        <v>7.3565729999999996E-2</v>
+      </c>
+      <c r="C77">
+        <v>0.81115122299999998</v>
+      </c>
+      <c r="D77">
+        <v>12.64923857868018</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>89.245431472081791</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>1</v>
+      </c>
+      <c r="B78">
         <v>9.1106320000000005E-2</v>
       </c>
-      <c r="B21">
+      <c r="C78">
         <v>1.9513685999999999E-2</v>
       </c>
-      <c r="C21">
-        <v>2674.6865482233511</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22">
+      <c r="D78">
+        <v>11.2558375634518</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>85.576142131980333</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>1</v>
+      </c>
+      <c r="B79">
         <v>2.4810392000000001E-2</v>
       </c>
-      <c r="B22">
+      <c r="C79">
         <v>0.95556558700000005</v>
       </c>
-      <c r="C22">
-        <v>2662.8980541455162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
+      <c r="D79">
+        <v>4.1700507614212832</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>84.275380710660016</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>1</v>
+      </c>
+      <c r="B80">
+        <v>2.4810392000000001E-2</v>
+      </c>
+      <c r="C80">
+        <v>0.95556558700000005</v>
+      </c>
+      <c r="D80">
+        <v>4.2746192893400803</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>74.164213197969303</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>1</v>
+      </c>
+      <c r="B81">
+        <v>9.1106320000000005E-2</v>
+      </c>
+      <c r="C81">
+        <v>1.9513685999999999E-2</v>
+      </c>
+      <c r="D81">
+        <v>12.784771573604081</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>57.84847715736084</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>1</v>
+      </c>
+      <c r="B82">
+        <v>6.8150700000000003E-3</v>
+      </c>
+      <c r="C82">
+        <v>0.30638246699999999</v>
+      </c>
+      <c r="D82">
+        <v>1.248223350253802</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>50.236802030457291</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>1</v>
+      </c>
+      <c r="B83">
+        <v>9.1106320000000005E-2</v>
+      </c>
+      <c r="C83">
+        <v>1.9513685999999999E-2</v>
+      </c>
+      <c r="D83">
+        <v>9.3888324873096849</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>37.113959390864387</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>1</v>
+      </c>
+      <c r="B84">
         <v>1.7124029999999998E-2</v>
       </c>
-      <c r="B23">
+      <c r="C84">
         <v>3.9181740999999999E-2</v>
       </c>
-      <c r="C23">
-        <v>2613.132402707276</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
+      <c r="D84">
+        <v>2.7401015228426222</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>28.456091370559079</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>1</v>
+      </c>
+      <c r="B85">
+        <v>6.8150700000000003E-3</v>
+      </c>
+      <c r="C85">
+        <v>0.30638246699999999</v>
+      </c>
+      <c r="D85">
+        <v>0.77258883248732246</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0.83934010152308325</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>1</v>
+      </c>
+      <c r="B86">
         <v>6.4509233999999999E-2</v>
       </c>
-      <c r="B24">
+      <c r="C86">
         <v>6.7372212000000001E-2</v>
       </c>
-      <c r="C24">
-        <v>2586.950930626057</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="D86">
+        <v>6.2431472081218624</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>-4.6355329949232758</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>1</v>
+      </c>
+      <c r="B87">
+        <v>1.7124029999999998E-2</v>
+      </c>
+      <c r="C87">
+        <v>3.9181740999999999E-2</v>
+      </c>
+      <c r="D87">
+        <v>2.539086294416244</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>-11.27258883248675</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>1</v>
+      </c>
+      <c r="B88">
+        <v>2.4810392000000001E-2</v>
+      </c>
+      <c r="C88">
+        <v>0.95556558700000005</v>
+      </c>
+      <c r="D88">
+        <v>4.1908629441624221</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>-16.855837563451271</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>1</v>
+      </c>
+      <c r="B89">
+        <v>1.7124029999999998E-2</v>
+      </c>
+      <c r="C89">
+        <v>3.9181740999999999E-2</v>
+      </c>
+      <c r="D89">
+        <v>1.7279187817258621</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>-22.447208121827551</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>1</v>
+      </c>
+      <c r="B90">
+        <v>6.4509233999999999E-2</v>
+      </c>
+      <c r="C90">
+        <v>6.7372212000000001E-2</v>
+      </c>
+      <c r="D90">
+        <v>7.382233502538103</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>-28.700000000000319</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>1</v>
+      </c>
+      <c r="B91">
         <v>1.0632783999999999E-2</v>
       </c>
-      <c r="B25">
+      <c r="C91">
         <v>4.6265971000000003E-2</v>
       </c>
-      <c r="C25">
-        <v>2535.887478849409</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26">
+      <c r="D91">
+        <v>1.1182741116751631</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>-44.671827411167577</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>1</v>
+      </c>
+      <c r="B92">
+        <v>1.0632783999999999E-2</v>
+      </c>
+      <c r="C92">
+        <v>4.6265971000000003E-2</v>
+      </c>
+      <c r="D92">
+        <v>1.3030456852792189</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>-52.419289340101081</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>1</v>
+      </c>
+      <c r="B93">
+        <v>6.4509233999999999E-2</v>
+      </c>
+      <c r="C93">
+        <v>6.7372212000000001E-2</v>
+      </c>
+      <c r="D93">
+        <v>7.7624365482233424</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>-53.99644670050688</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>1</v>
+      </c>
+      <c r="B94">
+        <v>2.4810392000000001E-2</v>
+      </c>
+      <c r="C94">
+        <v>0.95556558700000005</v>
+      </c>
+      <c r="D94">
+        <v>1.498984771573578</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>-67.731725888324917</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95">
+        <v>6.4509233999999999E-2</v>
+      </c>
+      <c r="C95">
+        <v>6.7372212000000001E-2</v>
+      </c>
+      <c r="D95">
+        <v>7.4086294416243419</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>-83.118781725887786</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>1</v>
+      </c>
+      <c r="B96">
+        <v>8.5529070000000002E-3</v>
+      </c>
+      <c r="C96">
+        <v>6.8391390000000002E-3</v>
+      </c>
+      <c r="D96">
+        <v>0.33654822335025969</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>-85.198223350253329</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>1</v>
+      </c>
+      <c r="B97">
+        <v>1.0632783999999999E-2</v>
+      </c>
+      <c r="C97">
+        <v>4.6265971000000003E-2</v>
+      </c>
+      <c r="D97">
+        <v>0.31319796954318241</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>-93.087309644669659</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>1</v>
+      </c>
+      <c r="B98">
+        <v>1.0632783999999999E-2</v>
+      </c>
+      <c r="C98">
+        <v>4.6265971000000003E-2</v>
+      </c>
+      <c r="D98">
+        <v>0.89746192893400334</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>-94.030203045684402</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>1</v>
+      </c>
+      <c r="B99">
+        <v>2.0868612000000002E-2</v>
+      </c>
+      <c r="C99">
+        <v>2.8246804E-2</v>
+      </c>
+      <c r="D99">
+        <v>2.713705583756322</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>-107.3109137055831</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>1</v>
+      </c>
+      <c r="B100">
         <v>2.9894693E-2</v>
       </c>
-      <c r="B26">
+      <c r="C100">
         <v>1.7273917E-2</v>
       </c>
-      <c r="C26">
-        <v>2479.8464467005078</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27">
+      <c r="D100">
+        <v>1.326395939086279</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>-117.7236040609137</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>1</v>
+      </c>
+      <c r="B101">
+        <v>8.5529070000000002E-3</v>
+      </c>
+      <c r="C101">
+        <v>6.8391390000000002E-3</v>
+      </c>
+      <c r="D101">
+        <v>-5.4822335025374258E-2</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>-132.39213197969539</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102">
+        <v>2.9894693E-2</v>
+      </c>
+      <c r="C102">
+        <v>1.7273917E-2</v>
+      </c>
+      <c r="D102">
+        <v>2.0568527918781392</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>-141.00862944162381</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>1</v>
+      </c>
+      <c r="B103">
+        <v>2.9894693E-2</v>
+      </c>
+      <c r="C103">
+        <v>1.7273917E-2</v>
+      </c>
+      <c r="D103">
+        <v>1.605583756345162</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>-146.88071065989769</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>1</v>
+      </c>
+      <c r="B104">
         <v>2.0868612000000002E-2</v>
       </c>
-      <c r="B27">
+      <c r="C104">
         <v>2.8246804E-2</v>
       </c>
-      <c r="C27">
-        <v>2472.2301184433172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="D104">
+        <v>2.3289340101523019</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>-150.67842639593829</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>1</v>
+      </c>
+      <c r="B105">
         <v>8.5529070000000002E-3</v>
       </c>
-      <c r="B28">
+      <c r="C105">
         <v>6.8391390000000002E-3</v>
       </c>
-      <c r="C28">
-        <v>2453.4813874788501</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29">
+      <c r="D105">
+        <v>-0.61827411167512025</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>-162.03350253807031</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>1</v>
+      </c>
+      <c r="B106">
+        <v>2.0868612000000002E-2</v>
+      </c>
+      <c r="C106">
+        <v>2.8246804E-2</v>
+      </c>
+      <c r="D106">
+        <v>3.465989847715782</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>-171.76243654822281</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>1</v>
+      </c>
+      <c r="B107">
+        <v>2.9894693E-2</v>
+      </c>
+      <c r="C107">
+        <v>1.7273917E-2</v>
+      </c>
+      <c r="D107">
+        <v>1.0010152284263609</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>-195.03350253807119</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>1</v>
+      </c>
+      <c r="B108">
+        <v>8.5529070000000002E-3</v>
+      </c>
+      <c r="C108">
+        <v>6.8391390000000002E-3</v>
+      </c>
+      <c r="D108">
+        <v>-0.69695431472081992</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>-197.66319796954269</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>1</v>
+      </c>
+      <c r="B109">
         <v>0.10378702400000001</v>
       </c>
-      <c r="B29">
+      <c r="C109">
         <v>5.3095417999999998E-2</v>
       </c>
-      <c r="C29">
-        <v>2346.833333333333</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
+      <c r="D109">
+        <v>8.9025380710659832</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>-232.0093908629436</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>1</v>
+      </c>
+      <c r="B110">
+        <v>2.0868612000000002E-2</v>
+      </c>
+      <c r="C110">
+        <v>2.8246804E-2</v>
+      </c>
+      <c r="D110">
+        <v>0.8614213197969427</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>-235.8720812182741</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>1</v>
+      </c>
+      <c r="B111">
+        <v>0.10378702400000001</v>
+      </c>
+      <c r="C111">
+        <v>5.3095417999999998E-2</v>
+      </c>
+      <c r="D111">
+        <v>8.8548223350254034</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>-287.07944162436519</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>1</v>
+      </c>
+      <c r="B112">
+        <v>0.10378702400000001</v>
+      </c>
+      <c r="C112">
+        <v>5.3095417999999998E-2</v>
+      </c>
+      <c r="D112">
+        <v>11.55177664974619</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>-288.23781725888273</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>1</v>
+      </c>
+      <c r="B113">
         <v>4.7063973000000002E-2</v>
       </c>
-      <c r="B30">
+      <c r="C113">
         <v>0.48010493199999998</v>
       </c>
-      <c r="C30">
-        <v>2266.3388324873099</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31">
+      <c r="D113">
+        <v>3.0928934010152389</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>-315.42563451776567</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>1</v>
+      </c>
+      <c r="B114">
+        <v>4.7063973000000002E-2</v>
+      </c>
+      <c r="C114">
+        <v>0.48010493199999998</v>
+      </c>
+      <c r="D114">
+        <v>3.8411167512690412</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>-336.76421319796901</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>1</v>
+      </c>
+      <c r="B115">
         <v>1.3823092E-2</v>
       </c>
-      <c r="B31">
+      <c r="C115">
         <v>7.7940129999999998E-3</v>
       </c>
-      <c r="C31">
-        <v>2254.8747884940781</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32">
+      <c r="D115">
+        <v>-1.6847715736040809</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>-354.78807106598981</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>1</v>
+      </c>
+      <c r="B116">
+        <v>1.3823092E-2</v>
+      </c>
+      <c r="C116">
+        <v>7.7940129999999998E-3</v>
+      </c>
+      <c r="D116">
+        <v>-1.3055837563451791</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>-362.54035532994868</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>1</v>
+      </c>
+      <c r="B117">
+        <v>0.10378702400000001</v>
+      </c>
+      <c r="C117">
+        <v>5.3095417999999998E-2</v>
+      </c>
+      <c r="D117">
+        <v>7.8172588832487619</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>-364.4350253807097</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>1</v>
+      </c>
+      <c r="B118">
+        <v>3.7491824E-2</v>
+      </c>
+      <c r="C118">
+        <v>7.8953589000000005E-2</v>
+      </c>
+      <c r="D118">
+        <v>0.50659898477156418</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>-368.02588832487271</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>1</v>
+      </c>
+      <c r="B119">
+        <v>1.3823092E-2</v>
+      </c>
+      <c r="C119">
+        <v>7.7940129999999998E-3</v>
+      </c>
+      <c r="D119">
+        <v>-2.2989847715736218</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>-368.49365482233469</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>1</v>
+      </c>
+      <c r="B120">
+        <v>4.7063973000000002E-2</v>
+      </c>
+      <c r="C120">
+        <v>0.48010493199999998</v>
+      </c>
+      <c r="D120">
+        <v>1.022335025380684</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>-393.53324873096432</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>1</v>
+      </c>
+      <c r="B121">
+        <v>1.3823092E-2</v>
+      </c>
+      <c r="C121">
+        <v>7.7940129999999998E-3</v>
+      </c>
+      <c r="D121">
+        <v>-2.6979695431471988</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>-405.00076142131928</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>1</v>
+      </c>
+      <c r="B122">
+        <v>3.7491824E-2</v>
+      </c>
+      <c r="C122">
+        <v>7.8953589000000005E-2</v>
+      </c>
+      <c r="D122">
+        <v>0.87614213197970514</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>-413.91065989847641</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>1</v>
+      </c>
+      <c r="B123">
+        <v>4.7063973000000002E-2</v>
+      </c>
+      <c r="C123">
+        <v>0.48010493199999998</v>
+      </c>
+      <c r="D123">
+        <v>1.211167512690402</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>-417.40837563451788</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>1</v>
+      </c>
+      <c r="B124">
         <v>8.0446389999999993E-3</v>
       </c>
-      <c r="B32">
+      <c r="C124">
         <v>9.3584130000000001E-2</v>
       </c>
-      <c r="C32">
-        <v>2135.6861252115059</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33">
+      <c r="D124">
+        <v>-3.256345177664997</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>-464.55228426395911</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>1</v>
+      </c>
+      <c r="B125">
+        <v>8.0446389999999993E-3</v>
+      </c>
+      <c r="C125">
+        <v>9.3584130000000001E-2</v>
+      </c>
+      <c r="D125">
+        <v>-3.2659898477157192</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>-485.70786802030392</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>1</v>
+      </c>
+      <c r="B126">
+        <v>8.0446389999999993E-3</v>
+      </c>
+      <c r="C126">
+        <v>9.3584130000000001E-2</v>
+      </c>
+      <c r="D126">
+        <v>-3.3309644670050602</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>-492.82081218274033</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>1</v>
+      </c>
+      <c r="B127">
         <v>3.7491824E-2</v>
       </c>
-      <c r="B33">
+      <c r="C127">
         <v>7.8953589000000005E-2</v>
       </c>
-      <c r="C33">
-        <v>2134.735194585448</v>
+      <c r="D127">
+        <v>-0.77868020304567764</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>-503.9799492385784</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>1</v>
+      </c>
+      <c r="B128">
+        <v>3.7491824E-2</v>
+      </c>
+      <c r="C128">
+        <v>7.8953589000000005E-2</v>
+      </c>
+      <c r="D128">
+        <v>-0.58934010152283989</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>-521.33121827411162</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>1</v>
+      </c>
+      <c r="B129">
+        <v>8.0446389999999993E-3</v>
+      </c>
+      <c r="C129">
+        <v>9.3584130000000001E-2</v>
+      </c>
+      <c r="D129">
+        <v>-3.739593908629459</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>-546.08375634517722</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C33">
-    <sortCondition descending="1" ref="C1:C33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G129">
+    <sortCondition descending="1" ref="G1:G129"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/May_5_full_log/LHS_HRP_1_res.xlsx
+++ b/May_5_full_log/LHS_HRP_1_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\May_5_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFCA501-D209-4DF8-8B54-732904EC38A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05F7D80-2E31-45F2-BCE1-0C35E33B9C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1529,10 +1529,10 @@
         <v>11.62436548223352</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>0.97967685589519593</v>
       </c>
       <c r="G49">
         <v>837.77461928934054</v>
@@ -1575,10 +1575,10 @@
         <v>13.538578680203059</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>0.20370439803531959</v>
       </c>
       <c r="G51">
         <v>706.43350253807171</v>
@@ -1621,10 +1621,10 @@
         <v>10.52588832487308</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>0.27173996913580301</v>
       </c>
       <c r="G53">
         <v>659.26319796954351</v>
@@ -1644,10 +1644,10 @@
         <v>11.60761421319796</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>0.909012988148861</v>
       </c>
       <c r="G54">
         <v>586.36091370558404</v>
@@ -1736,10 +1736,10 @@
         <v>7.054314720812183</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>0.15338562279628831</v>
       </c>
       <c r="G58">
         <v>432.16624365482272</v>
@@ -1759,10 +1759,10 @@
         <v>7.185279187817244</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>4.7827622748146573E-2</v>
       </c>
       <c r="G59">
         <v>387.09010152284282</v>
@@ -1897,10 +1897,10 @@
         <v>11.681218274111689</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>0.187458717191029</v>
       </c>
       <c r="G65">
         <v>222.28274111675191</v>
@@ -2058,10 +2058,10 @@
         <v>13.066497461928961</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>0.1240666640767638</v>
       </c>
       <c r="G72">
         <v>134.39619289340109</v>
@@ -2127,10 +2127,10 @@
         <v>12.90253807106598</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>8.1902588716657912E-2</v>
       </c>
       <c r="G75">
         <v>111.3449238578683</v>
@@ -2150,10 +2150,10 @@
         <v>9.3106598984771871</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>8.9019736124740859E-2</v>
       </c>
       <c r="G76">
         <v>89.690101522842937</v>
@@ -2173,10 +2173,10 @@
         <v>12.64923857868018</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>5.5291143304306282E-2</v>
       </c>
       <c r="G77">
         <v>89.245431472081791</v>
@@ -2196,10 +2196,10 @@
         <v>11.2558375634518</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>0.127861459366827</v>
       </c>
       <c r="G78">
         <v>85.576142131980333</v>
@@ -2265,10 +2265,10 @@
         <v>12.784771573604081</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>8.6008099737949706E-2</v>
       </c>
       <c r="G81">
         <v>57.84847715736084</v>
@@ -2311,10 +2311,10 @@
         <v>9.3888324873096849</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>9.48637543252593E-2</v>
       </c>
       <c r="G83">
         <v>37.113959390864387</v>
@@ -2380,10 +2380,10 @@
         <v>6.2431472081218624</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>0.25480120334986539</v>
       </c>
       <c r="G86">
         <v>-4.6355329949232758</v>
@@ -2472,10 +2472,10 @@
         <v>7.382233502538103</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>0.1222168740975</v>
       </c>
       <c r="G90">
         <v>-28.700000000000319</v>
@@ -2541,10 +2541,10 @@
         <v>7.7624365482233424</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>6.7499346063303198E-2</v>
       </c>
       <c r="G93">
         <v>-53.99644670050688</v>
@@ -2587,10 +2587,10 @@
         <v>7.4086294416243419</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>3.2106885919835723E-2</v>
       </c>
       <c r="G95">
         <v>-83.118781725887786</v>
@@ -2909,7 +2909,7 @@
         <v>8.9025380710659832</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         <v>8.8548223350254034</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>11.55177664974619</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>7.8172588832487619</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117">
         <v>0</v>
